--- a/data/trans_orig/P24D-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P24D-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2007</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2007 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63548</t>
+          <t>63020</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92455</t>
+          <t>92832</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19583</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38221</t>
+          <t>38453</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88900</t>
+          <t>89905</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124094</t>
+          <t>126297</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224796</t>
+          <t>224419</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>253703</t>
+          <t>254231</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117753</t>
+          <t>117521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136391</t>
+          <t>135493</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>349131</t>
+          <t>346928</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>384325</t>
+          <t>383320</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,0%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108487</t>
+          <t>109643</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145391</t>
+          <t>148084</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80602</t>
+          <t>81096</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111578</t>
+          <t>110806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>197733</t>
+          <t>194703</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>246297</t>
+          <t>245438</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>259920</t>
+          <t>257227</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>296824</t>
+          <t>295668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113463</t>
+          <t>114235</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>144439</t>
+          <t>143945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>384055</t>
+          <t>384914</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>432619</t>
+          <t>435649</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77952</t>
+          <t>78228</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>112420</t>
+          <t>110100</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54683</t>
+          <t>54220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78572</t>
+          <t>79016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143635</t>
+          <t>140270</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185520</t>
+          <t>181030</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>141555</t>
+          <t>143875</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>176023</t>
+          <t>175747</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90493</t>
+          <t>90049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114382</t>
+          <t>114845</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>237520</t>
+          <t>242010</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>279405</t>
+          <t>282770</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>102788</t>
+          <t>104069</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>137508</t>
+          <t>139003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92690</t>
+          <t>91028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126666</t>
+          <t>125621</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204044</t>
+          <t>205896</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>255500</t>
+          <t>255135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>266783</t>
+          <t>265288</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>301503</t>
+          <t>300222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>177728</t>
+          <t>178773</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>211704</t>
+          <t>213366</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>453185</t>
+          <t>453550</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>504641</t>
+          <t>502789</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>384310</t>
+          <t>387290</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>454734</t>
+          <t>456308</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>272592</t>
+          <t>268931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>326520</t>
+          <t>323551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>671967</t>
+          <t>671062</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>767700</t>
+          <t>759321</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>926094</t>
+          <t>924520</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>996518</t>
+          <t>993538</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>527954</t>
+          <t>530923</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>581882</t>
+          <t>585543</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1467602</t>
+          <t>1475981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1563335</t>
+          <t>1564240</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,98%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2012</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2012 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>114538</t>
+          <t>112783</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147972</t>
+          <t>148145</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83489</t>
+          <t>83795</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>109103</t>
+          <t>108744</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>204988</t>
+          <t>206919</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>247178</t>
+          <t>247797</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,44%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121611</t>
+          <t>121438</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155045</t>
+          <t>156800</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52737</t>
+          <t>53096</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78351</t>
+          <t>78045</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>184245</t>
+          <t>183626</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>226435</t>
+          <t>224504</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,04%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178835</t>
+          <t>178596</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>221300</t>
+          <t>220663</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131901</t>
+          <t>132635</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>166352</t>
+          <t>167754</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>320099</t>
+          <t>324602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>375006</t>
+          <t>377457</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,24%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>184198</t>
+          <t>184835</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226663</t>
+          <t>226902</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>123995</t>
+          <t>122593</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>158446</t>
+          <t>157712</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>320840</t>
+          <t>318389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>375747</t>
+          <t>371244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128908</t>
+          <t>127752</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>167044</t>
+          <t>166656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100206</t>
+          <t>99861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133280</t>
+          <t>131584</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>239429</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>290261</t>
+          <t>288625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,34%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145429</t>
+          <t>145817</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>183565</t>
+          <t>184721</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95337</t>
+          <t>97033</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128411</t>
+          <t>128756</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>250830</t>
+          <t>252466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>301662</t>
+          <t>301703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132328</t>
+          <t>129724</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>169143</t>
+          <t>167103</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114846</t>
+          <t>118526</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150947</t>
+          <t>153227</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>259207</t>
+          <t>256440</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>312353</t>
+          <t>306825</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195194</t>
+          <t>197234</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>232009</t>
+          <t>234613</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137442</t>
+          <t>135162</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>173543</t>
+          <t>169863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340374</t>
+          <t>345902</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>393520</t>
+          <t>396287</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>590891</t>
+          <t>588595</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>663949</t>
+          <t>664147</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>467390</t>
+          <t>463910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>530327</t>
+          <t>527689</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1066822</t>
+          <t>1075336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1170387</t>
+          <t>1178002</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>687943</t>
+          <t>687745</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>761001</t>
+          <t>763297</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>438867</t>
+          <t>441505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>501804</t>
+          <t>505284</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1150699</t>
+          <t>1143084</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1254264</t>
+          <t>1245750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2016</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2016 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95711</t>
+          <t>92902</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127827</t>
+          <t>126619</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54914</t>
+          <t>54720</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80651</t>
+          <t>79536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>159151</t>
+          <t>158338</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>200756</t>
+          <t>199032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>122725</t>
+          <t>123933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154841</t>
+          <t>157650</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87758</t>
+          <t>88873</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113495</t>
+          <t>113689</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>218205</t>
+          <t>219929</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>259810</t>
+          <t>260623</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>141790</t>
+          <t>140410</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>178115</t>
+          <t>178431</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>127705</t>
+          <t>127498</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160616</t>
+          <t>161630</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>276394</t>
+          <t>276904</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>330019</t>
+          <t>329047</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,32%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>156673</t>
+          <t>156357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>192998</t>
+          <t>194378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>110312</t>
+          <t>109298</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>143223</t>
+          <t>143430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>275697</t>
+          <t>276669</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>329322</t>
+          <t>328812</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,28%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94357</t>
+          <t>94229</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129430</t>
+          <t>129754</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60693</t>
+          <t>59388</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88591</t>
+          <t>87533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>162179</t>
+          <t>161321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>208091</t>
+          <t>205608</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>179580</t>
+          <t>179256</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>214653</t>
+          <t>214781</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136666</t>
+          <t>137724</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164564</t>
+          <t>165869</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>326176</t>
+          <t>328659</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>372088</t>
+          <t>372946</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,81%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104685</t>
+          <t>106993</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139272</t>
+          <t>140243</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109923</t>
+          <t>109788</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>143740</t>
+          <t>142748</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223696</t>
+          <t>225737</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>272346</t>
+          <t>271711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142516</t>
+          <t>141545</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177103</t>
+          <t>174795</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113644</t>
+          <t>114636</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147461</t>
+          <t>147596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>267461</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>315476</t>
+          <t>313435</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>467578</t>
+          <t>470680</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>534850</t>
+          <t>539975</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>377594</t>
+          <t>379914</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>439527</t>
+          <t>442177</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>868127</t>
+          <t>868049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>960933</t>
+          <t>964351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>641287</t>
+          <t>636162</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>708559</t>
+          <t>705457</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>482452</t>
+          <t>479802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>544385</t>
+          <t>542065</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1137183</t>
+          <t>1133765</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1229989</t>
+          <t>1230067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,63%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2023</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2023 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47074</t>
+          <t>46040</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74402</t>
+          <t>73791</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36784</t>
+          <t>35818</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55146</t>
+          <t>54398</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88349</t>
+          <t>87628</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122641</t>
+          <t>121786</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103615</t>
+          <t>104226</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130943</t>
+          <t>131977</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67377</t>
+          <t>68125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85739</t>
+          <t>86705</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>177899</t>
+          <t>178754</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>212191</t>
+          <t>212912</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,84%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62282</t>
+          <t>62256</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101253</t>
+          <t>98985</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66802</t>
+          <t>67241</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91319</t>
+          <t>91096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>134693</t>
+          <t>135078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180974</t>
+          <t>184002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135901</t>
+          <t>138169</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174872</t>
+          <t>174898</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>87865</t>
+          <t>88088</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112382</t>
+          <t>111943</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>235364</t>
+          <t>232336</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>281645</t>
+          <t>281260</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,56%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54826</t>
+          <t>53468</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84147</t>
+          <t>84311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53015</t>
+          <t>51443</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74473</t>
+          <t>74550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112698</t>
+          <t>113006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151548</t>
+          <t>154393</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>44,4%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>109997</t>
+          <t>109833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>139318</t>
+          <t>140676</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79120</t>
+          <t>79043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100578</t>
+          <t>102150</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>196189</t>
+          <t>193344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>235039</t>
+          <t>234731</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,5%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69481</t>
+          <t>71283</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99529</t>
+          <t>100516</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82257</t>
+          <t>81911</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106798</t>
+          <t>106006</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>158262</t>
+          <t>160532</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>196879</t>
+          <t>198289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,53%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117964</t>
+          <t>116977</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148012</t>
+          <t>146210</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84306</t>
+          <t>85098</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108847</t>
+          <t>109193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>211718</t>
+          <t>210308</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>250335</t>
+          <t>248065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>261761</t>
+          <t>263266</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>325962</t>
+          <t>325930</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>261133</t>
+          <t>259098</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>305334</t>
+          <t>304949</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>534770</t>
+          <t>533230</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>616261</t>
+          <t>613310</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>500846</t>
+          <t>500878</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>565047</t>
+          <t>563542</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>341071</t>
+          <t>341456</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>385272</t>
+          <t>387307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>856951</t>
+          <t>859902</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>938442</t>
+          <t>939982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24D-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P24D-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63020</t>
+          <t>63074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92832</t>
+          <t>95254</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38453</t>
+          <t>39453</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89905</t>
+          <t>88721</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>126297</t>
+          <t>125834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224419</t>
+          <t>221997</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>254231</t>
+          <t>254177</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117521</t>
+          <t>116521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135493</t>
+          <t>136303</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>346928</t>
+          <t>347391</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>383320</t>
+          <t>384504</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109643</t>
+          <t>108936</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148084</t>
+          <t>147157</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81096</t>
+          <t>79564</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110806</t>
+          <t>108945</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194703</t>
+          <t>199331</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>245438</t>
+          <t>247372</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>257227</t>
+          <t>258154</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>295668</t>
+          <t>296375</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>114235</t>
+          <t>116096</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>143945</t>
+          <t>145477</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>384914</t>
+          <t>382980</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>435649</t>
+          <t>431021</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,38%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78228</t>
+          <t>79040</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110100</t>
+          <t>111919</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54220</t>
+          <t>54420</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79016</t>
+          <t>79482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140270</t>
+          <t>141354</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181030</t>
+          <t>181599</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,93%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143875</t>
+          <t>142056</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>175747</t>
+          <t>174935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90049</t>
+          <t>89583</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114845</t>
+          <t>114645</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242010</t>
+          <t>241441</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>282770</t>
+          <t>281686</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,59%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104069</t>
+          <t>102812</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139003</t>
+          <t>139823</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91028</t>
+          <t>91607</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125621</t>
+          <t>126092</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>205896</t>
+          <t>205149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>255135</t>
+          <t>252327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>265288</t>
+          <t>264468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300222</t>
+          <t>301479</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>178773</t>
+          <t>178302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>213366</t>
+          <t>212787</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>453550</t>
+          <t>456358</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>502789</t>
+          <t>503536</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>387290</t>
+          <t>387022</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>456308</t>
+          <t>457836</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>268931</t>
+          <t>268296</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>323551</t>
+          <t>324646</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>671062</t>
+          <t>673899</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>759321</t>
+          <t>762196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>924520</t>
+          <t>922992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>993538</t>
+          <t>993806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>530923</t>
+          <t>529828</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>585543</t>
+          <t>586178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1475981</t>
+          <t>1473106</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1564240</t>
+          <t>1561403</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,85%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112783</t>
+          <t>112895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>148145</t>
+          <t>145527</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83795</t>
+          <t>83047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>108744</t>
+          <t>110961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>206919</t>
+          <t>203671</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>247797</t>
+          <t>248643</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121438</t>
+          <t>124056</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>156800</t>
+          <t>156688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53096</t>
+          <t>50879</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78045</t>
+          <t>78793</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>183626</t>
+          <t>182780</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>224504</t>
+          <t>227752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,79%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178596</t>
+          <t>177220</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220663</t>
+          <t>220266</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132635</t>
+          <t>131611</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167754</t>
+          <t>167169</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>324602</t>
+          <t>322457</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>377457</t>
+          <t>376529</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,11%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>184835</t>
+          <t>185232</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226902</t>
+          <t>228278</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122593</t>
+          <t>123178</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>157712</t>
+          <t>158736</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>318389</t>
+          <t>319317</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>371244</t>
+          <t>373389</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,66%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127752</t>
+          <t>129232</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>166656</t>
+          <t>165930</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99861</t>
+          <t>99604</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131584</t>
+          <t>131898</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>238878</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>288625</t>
+          <t>287567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,15%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145817</t>
+          <t>146543</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>184721</t>
+          <t>183241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97033</t>
+          <t>96719</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128756</t>
+          <t>129013</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>252466</t>
+          <t>253524</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>301703</t>
+          <t>302213</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,85%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>129724</t>
+          <t>130090</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>167103</t>
+          <t>166918</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118526</t>
+          <t>115720</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>153227</t>
+          <t>150566</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>256440</t>
+          <t>256609</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>306825</t>
+          <t>309564</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197234</t>
+          <t>197419</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>234613</t>
+          <t>234247</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135162</t>
+          <t>137823</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>169863</t>
+          <t>172669</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>345902</t>
+          <t>343163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>396287</t>
+          <t>396118</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,69%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>588595</t>
+          <t>587726</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>664147</t>
+          <t>662984</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>463910</t>
+          <t>461690</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>527689</t>
+          <t>528034</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1075336</t>
+          <t>1067264</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1178002</t>
+          <t>1169235</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>687745</t>
+          <t>688908</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>763297</t>
+          <t>764166</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>441505</t>
+          <t>441160</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>505284</t>
+          <t>507504</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1143084</t>
+          <t>1151851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1245750</t>
+          <t>1253822</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92902</t>
+          <t>95664</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>126619</t>
+          <t>127515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54720</t>
+          <t>54607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79536</t>
+          <t>79298</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>158338</t>
+          <t>160438</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199032</t>
+          <t>198709</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>123933</t>
+          <t>123037</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157650</t>
+          <t>154888</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88873</t>
+          <t>89111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113689</t>
+          <t>113802</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>219929</t>
+          <t>220252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>260623</t>
+          <t>258523</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,71%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>140410</t>
+          <t>141062</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>178431</t>
+          <t>178877</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>127498</t>
+          <t>126708</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>161630</t>
+          <t>160751</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>276904</t>
+          <t>278775</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>329047</t>
+          <t>328271</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,2%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>156357</t>
+          <t>155911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>194378</t>
+          <t>193726</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>109298</t>
+          <t>110177</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>143430</t>
+          <t>144220</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>276669</t>
+          <t>277445</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>328812</t>
+          <t>326941</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94229</t>
+          <t>94407</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129754</t>
+          <t>128466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59388</t>
+          <t>58401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87533</t>
+          <t>87563</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161321</t>
+          <t>162366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205608</t>
+          <t>208015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>179256</t>
+          <t>180544</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>214781</t>
+          <t>214603</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137724</t>
+          <t>137694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165869</t>
+          <t>166856</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>328659</t>
+          <t>326252</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>372946</t>
+          <t>371901</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,61%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106993</t>
+          <t>106534</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140243</t>
+          <t>139403</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109788</t>
+          <t>110220</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142748</t>
+          <t>141297</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>225737</t>
+          <t>226775</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>271711</t>
+          <t>271477</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141545</t>
+          <t>142385</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>174795</t>
+          <t>175254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114636</t>
+          <t>116087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147596</t>
+          <t>147164</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>267461</t>
+          <t>267695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313435</t>
+          <t>312397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>470680</t>
+          <t>470649</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>539975</t>
+          <t>540294</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>379914</t>
+          <t>381797</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>442177</t>
+          <t>441009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>868049</t>
+          <t>870043</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>964351</t>
+          <t>961813</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>636162</t>
+          <t>635843</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>705457</t>
+          <t>705488</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>479802</t>
+          <t>480970</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>542065</t>
+          <t>540182</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1133765</t>
+          <t>1136303</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1230067</t>
+          <t>1228073</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>59259</t>
+          <t>64207</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46040</t>
+          <t>51479</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73791</t>
+          <t>80502</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>44980</t>
+          <t>47725</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35818</t>
+          <t>38822</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54398</t>
+          <t>57577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>104239</t>
+          <t>111932</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87628</t>
+          <t>95908</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121786</t>
+          <t>131604</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,77%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>118758</t>
+          <t>128705</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104226</t>
+          <t>112410</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131977</t>
+          <t>141433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>77543</t>
+          <t>82167</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68125</t>
+          <t>72315</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86705</t>
+          <t>91070</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>196301</t>
+          <t>210872</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>178754</t>
+          <t>191200</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>212912</t>
+          <t>226896</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,29%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>178017</t>
+          <t>192912</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>178017</t>
+          <t>192912</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>178017</t>
+          <t>192912</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>122523</t>
+          <t>129892</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>122523</t>
+          <t>129892</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>122523</t>
+          <t>129892</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>300540</t>
+          <t>322804</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>300540</t>
+          <t>322804</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>300540</t>
+          <t>322804</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78837</t>
+          <t>81336</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62256</t>
+          <t>65694</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98985</t>
+          <t>100062</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>78976</t>
+          <t>84965</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67241</t>
+          <t>72988</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91096</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>157813</t>
+          <t>166301</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135078</t>
+          <t>140961</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>184002</t>
+          <t>187160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>41,7%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>158317</t>
+          <t>172716</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>138169</t>
+          <t>153990</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174898</t>
+          <t>188358</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>100208</t>
+          <t>109823</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88088</t>
+          <t>95455</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111943</t>
+          <t>121800</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>258525</t>
+          <t>282539</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>232336</t>
+          <t>261680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>281260</t>
+          <t>307879</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>68,59%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>237154</t>
+          <t>254052</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>237154</t>
+          <t>254052</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>237154</t>
+          <t>254052</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>179184</t>
+          <t>194788</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>179184</t>
+          <t>194788</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>179184</t>
+          <t>194788</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>416338</t>
+          <t>448840</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>416338</t>
+          <t>448840</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>416338</t>
+          <t>448840</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,102 +7255,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>68875</t>
+          <t>80128</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53468</t>
+          <t>64575</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84311</t>
+          <t>98443</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>38,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>31,07%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>47,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>72358</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>59648</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>84251</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>42,21%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>34,8%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>49,15%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>152486</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>134550</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>176387</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>40,21%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>35,48%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>63180</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>51443</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>74550</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>41,13%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>33,49%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>48,54%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>132056</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>113006</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>154393</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>37,98%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>32,5%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>46,51%</t>
         </is>
       </c>
     </row>
@@ -7368,102 +7368,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>125269</t>
+          <t>127710</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>109833</t>
+          <t>109395</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140676</t>
+          <t>143263</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>61,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>52,63%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>68,93%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>99046</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>87153</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>111756</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>57,79%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>50,85%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>65,2%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>226757</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>202856</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>244693</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>59,79%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>53,49%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>64,52%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>72,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>90413</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>79043</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>102150</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>58,87%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>51,46%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>66,51%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>215681</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>193344</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>234731</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>62,02%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>55,6%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>67,5%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>194144</t>
+          <t>207838</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>194144</t>
+          <t>207838</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>194144</t>
+          <t>207838</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>153593</t>
+          <t>171404</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>153593</t>
+          <t>171404</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>153593</t>
+          <t>171404</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>347737</t>
+          <t>379243</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>347737</t>
+          <t>379243</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>347737</t>
+          <t>379243</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>84323</t>
+          <t>94160</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71283</t>
+          <t>78731</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100516</t>
+          <t>112063</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>94572</t>
+          <t>101984</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81911</t>
+          <t>89488</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106006</t>
+          <t>115274</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>178895</t>
+          <t>196144</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160532</t>
+          <t>176315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198289</t>
+          <t>216227</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>133170</t>
+          <t>145398</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116977</t>
+          <t>127495</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146210</t>
+          <t>160827</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>96532</t>
+          <t>102877</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85098</t>
+          <t>89587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109193</t>
+          <t>115373</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>229702</t>
+          <t>248275</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>210308</t>
+          <t>228192</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>248065</t>
+          <t>268104</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,33%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>217493</t>
+          <t>239558</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>217493</t>
+          <t>239558</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>217493</t>
+          <t>239558</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>191104</t>
+          <t>204861</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>191104</t>
+          <t>204861</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>191104</t>
+          <t>204861</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>408597</t>
+          <t>444419</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>408597</t>
+          <t>444419</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>408597</t>
+          <t>444419</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>291294</t>
+          <t>319831</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>263266</t>
+          <t>285482</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>325930</t>
+          <t>353950</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>281709</t>
+          <t>307031</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>259098</t>
+          <t>282477</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>304949</t>
+          <t>329045</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>573003</t>
+          <t>626863</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>533230</t>
+          <t>588102</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>613310</t>
+          <t>669762</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,98%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>535514</t>
+          <t>574529</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>500878</t>
+          <t>540410</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>563542</t>
+          <t>608878</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>364696</t>
+          <t>393914</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>341456</t>
+          <t>371900</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>387307</t>
+          <t>418468</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>900209</t>
+          <t>968443</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>859902</t>
+          <t>925544</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>939982</t>
+          <t>1007204</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,14%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>826808</t>
+          <t>894360</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>826808</t>
+          <t>894360</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>826808</t>
+          <t>894360</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>646405</t>
+          <t>700945</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>646405</t>
+          <t>700945</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>646405</t>
+          <t>700945</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1473212</t>
+          <t>1595306</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1473212</t>
+          <t>1595306</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1473212</t>
+          <t>1595306</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
